--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679938</v>
+        <v>113679936</v>
       </c>
       <c r="B2" t="n">
-        <v>90128</v>
+        <v>90130</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillmyran, Ång</t>
+          <t>Nipliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641825</v>
+        <v>641739</v>
       </c>
       <c r="R2" t="n">
-        <v>7074580</v>
+        <v>7074609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679935</v>
+        <v>113679938</v>
       </c>
       <c r="B3" t="n">
-        <v>90146</v>
+        <v>90130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nipliden, Ång</t>
+          <t>Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641739</v>
+        <v>641825</v>
       </c>
       <c r="R3" t="n">
-        <v>7074609</v>
+        <v>7074580</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679936</v>
+        <v>113679935</v>
       </c>
       <c r="B4" t="n">
-        <v>90128</v>
+        <v>90148</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
         <v>113679930</v>
       </c>
       <c r="B5" t="n">
-        <v>90690</v>
+        <v>90692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679936</v>
       </c>
       <c r="B2" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>113679938</v>
       </c>
       <c r="B3" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>113679935</v>
       </c>
       <c r="B4" t="n">
-        <v>90148</v>
+        <v>90149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>113679930</v>
       </c>
       <c r="B5" t="n">
-        <v>90692</v>
+        <v>90693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679936</v>
+        <v>113679935</v>
       </c>
       <c r="B2" t="n">
-        <v>90131</v>
+        <v>90153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679938</v>
+        <v>113679930</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>90697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillmyran, Ång</t>
+          <t>Nipliden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641825</v>
+        <v>641731</v>
       </c>
       <c r="R3" t="n">
-        <v>7074580</v>
+        <v>7074723</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679935</v>
+        <v>113679938</v>
       </c>
       <c r="B4" t="n">
-        <v>90149</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nipliden, Ång</t>
+          <t>Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641739</v>
+        <v>641825</v>
       </c>
       <c r="R4" t="n">
-        <v>7074609</v>
+        <v>7074580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679930</v>
+        <v>113679936</v>
       </c>
       <c r="B5" t="n">
-        <v>90693</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641731</v>
+        <v>641739</v>
       </c>
       <c r="R5" t="n">
-        <v>7074723</v>
+        <v>7074609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679935</v>
+        <v>113679938</v>
       </c>
       <c r="B2" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nipliden, Ång</t>
+          <t>Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641739</v>
+        <v>641825</v>
       </c>
       <c r="R2" t="n">
-        <v>7074609</v>
+        <v>7074580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679938</v>
+        <v>113679935</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillmyran, Ång</t>
+          <t>Nipliden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641825</v>
+        <v>641739</v>
       </c>
       <c r="R4" t="n">
-        <v>7074580</v>
+        <v>7074609</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679938</v>
+        <v>113679936</v>
       </c>
       <c r="B2" t="n">
         <v>90135</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillmyran, Ång</t>
+          <t>Nipliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641825</v>
+        <v>641739</v>
       </c>
       <c r="R2" t="n">
-        <v>7074580</v>
+        <v>7074609</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679936</v>
+        <v>113679938</v>
       </c>
       <c r="B5" t="n">
         <v>90135</v>
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nipliden, Ång</t>
+          <t>Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641739</v>
+        <v>641825</v>
       </c>
       <c r="R5" t="n">
-        <v>7074609</v>
+        <v>7074580</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679936</v>
+        <v>113679938</v>
       </c>
       <c r="B2" t="n">
         <v>90135</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nipliden, Ång</t>
+          <t>Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641739</v>
+        <v>641825</v>
       </c>
       <c r="R2" t="n">
-        <v>7074609</v>
+        <v>7074580</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679938</v>
+        <v>113679936</v>
       </c>
       <c r="B5" t="n">
         <v>90135</v>
@@ -1044,14 +1044,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillmyran, Ång</t>
+          <t>Nipliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>641825</v>
+        <v>641739</v>
       </c>
       <c r="R5" t="n">
-        <v>7074580</v>
+        <v>7074609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113679938</v>
+        <v>113679930</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillmyran, Ång</t>
+          <t>Nipliden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>641825</v>
+        <v>641731</v>
       </c>
       <c r="R2" t="n">
-        <v>7074580</v>
+        <v>7074723</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113679930</v>
+        <v>113679936</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>641731</v>
+        <v>641739</v>
       </c>
       <c r="R3" t="n">
-        <v>7074723</v>
+        <v>7074609</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113679935</v>
+        <v>113679938</v>
       </c>
       <c r="B4" t="n">
-        <v>90153</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nipliden, Ång</t>
+          <t>Lillmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>641739</v>
+        <v>641825</v>
       </c>
       <c r="R4" t="n">
-        <v>7074609</v>
+        <v>7074580</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113679936</v>
+        <v>113679935</v>
       </c>
       <c r="B5" t="n">
-        <v>90135</v>
+        <v>90153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>122753448</v>
       </c>
       <c r="B6" t="n">
-        <v>91289</v>
+        <v>91293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>122753448</v>
       </c>
       <c r="B6" t="n">
-        <v>91293</v>
+        <v>91301</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>122753448</v>
       </c>
       <c r="B6" t="n">
-        <v>91301</v>
+        <v>91304</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 53482-2023 artfynd.xlsx
+++ b/artfynd/A 53482-2023 artfynd.xlsx
@@ -1122,7 +1122,7 @@
         <v>122753448</v>
       </c>
       <c r="B6" t="n">
-        <v>91304</v>
+        <v>91306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
